--- a/union_master.xlsx
+++ b/union_master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\012796524\Dropbox\Research Projects\SASB 2\SASB Project\Data and Descriptive\BLS Union Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sjsu0-my.sharepoint.com/personal/suzanne_haley_sjsu_edu/Documents/Documents/GitHub/Data-and-Coding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0F4CEA-3B34-4EF1-896D-39741EA984B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7C0F4CEA-3B34-4EF1-896D-39741EA984B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E81977FB-4101-4037-92FE-F13756316A27}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="raw_data" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -238,7 +238,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -260,12 +260,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -313,8 +319,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3406,7 +3414,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B82D392A-F69F-4065-AD72-6A25EEC0F057}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B82D392A-F69F-4065-AD72-6A25EEC0F057}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:D114" firstHeaderRow="0" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4187,10 +4195,10 @@
       <c r="A3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="9" t="s">
@@ -12184,10 +12192,10 @@
       <c r="B4">
         <v>2016</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4">
         <v>24051</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4">
         <v>1248</v>
       </c>
     </row>
@@ -12198,10 +12206,10 @@
       <c r="B5">
         <v>2017</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5">
         <v>24255</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5">
         <v>1331</v>
       </c>
     </row>
@@ -12212,10 +12220,10 @@
       <c r="B6">
         <v>2018</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6">
         <v>24196</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6">
         <v>1296</v>
       </c>
     </row>
@@ -12226,10 +12234,10 @@
       <c r="B7">
         <v>2019</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7">
         <v>23681</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7">
         <v>1196</v>
       </c>
     </row>
@@ -12240,10 +12248,10 @@
       <c r="B8">
         <v>2020</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8">
         <v>22590</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8">
         <v>1215</v>
       </c>
     </row>
@@ -12254,10 +12262,10 @@
       <c r="B9">
         <v>2021</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9">
         <v>23218</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9">
         <v>1183</v>
       </c>
     </row>
@@ -12268,10 +12276,10 @@
       <c r="B10">
         <v>2022</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10">
         <v>23139</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10">
         <v>1140</v>
       </c>
     </row>
@@ -12282,10 +12290,10 @@
       <c r="B11">
         <v>2023</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11">
         <v>23335</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11">
         <v>1109</v>
       </c>
     </row>
@@ -12296,10 +12304,10 @@
       <c r="B12">
         <v>2024</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12">
         <v>23111</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12">
         <v>1143</v>
       </c>
     </row>
@@ -12310,10 +12318,10 @@
       <c r="B13">
         <v>2025</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13">
         <v>23115</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13">
         <v>1193</v>
       </c>
     </row>
@@ -12324,10 +12332,10 @@
       <c r="B14">
         <v>2016</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14">
         <v>765</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14">
         <v>43</v>
       </c>
     </row>
@@ -12338,10 +12346,10 @@
       <c r="B15">
         <v>2017</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15">
         <v>735</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15">
         <v>32</v>
       </c>
     </row>
@@ -12352,10 +12360,10 @@
       <c r="B16">
         <v>2018</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16">
         <v>721</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16">
         <v>34</v>
       </c>
     </row>
@@ -12366,10 +12374,10 @@
       <c r="B17">
         <v>2019</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17">
         <v>710</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17">
         <v>28</v>
       </c>
     </row>
@@ -12380,10 +12388,10 @@
       <c r="B18">
         <v>2020</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18">
         <v>656</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18">
         <v>37</v>
       </c>
     </row>
@@ -12394,10 +12402,10 @@
       <c r="B19">
         <v>2021</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19">
         <v>561</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19">
         <v>32</v>
       </c>
     </row>
@@ -12408,10 +12416,10 @@
       <c r="B20">
         <v>2022</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20">
         <v>556</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20">
         <v>36</v>
       </c>
     </row>
@@ -12422,10 +12430,10 @@
       <c r="B21">
         <v>2023</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21">
         <v>577</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21">
         <v>25</v>
       </c>
     </row>
@@ -12436,10 +12444,10 @@
       <c r="B22">
         <v>2024</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22">
         <v>538</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22">
         <v>35</v>
       </c>
     </row>
@@ -12450,10 +12458,10 @@
       <c r="B23">
         <v>2025</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23">
         <v>487</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23">
         <v>23</v>
       </c>
     </row>
@@ -12464,10 +12472,10 @@
       <c r="B24">
         <v>2016</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24">
         <v>8963</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24">
         <v>205</v>
       </c>
     </row>
@@ -12478,10 +12486,10 @@
       <c r="B25">
         <v>2017</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25">
         <v>9068</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25">
         <v>218</v>
       </c>
     </row>
@@ -12492,10 +12500,10 @@
       <c r="B26">
         <v>2018</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26">
         <v>9149</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26">
         <v>193</v>
       </c>
     </row>
@@ -12506,10 +12514,10 @@
       <c r="B27">
         <v>2019</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27">
         <v>9364</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27">
         <v>182</v>
       </c>
     </row>
@@ -12520,10 +12528,10 @@
       <c r="B28">
         <v>2020</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28">
         <v>9108</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28">
         <v>170</v>
       </c>
     </row>
@@ -12534,10 +12542,10 @@
       <c r="B29">
         <v>2021</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29">
         <v>9101</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29">
         <v>205</v>
       </c>
     </row>
@@ -12548,10 +12556,10 @@
       <c r="B30">
         <v>2022</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30">
         <v>9336</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30">
         <v>170</v>
       </c>
     </row>
@@ -12562,10 +12570,10 @@
       <c r="B31">
         <v>2023</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31">
         <v>9284</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31">
         <v>162</v>
       </c>
     </row>
@@ -12576,10 +12584,10 @@
       <c r="B32">
         <v>2024</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32">
         <v>9231</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32">
         <v>122</v>
       </c>
     </row>
@@ -12590,10 +12598,10 @@
       <c r="B33">
         <v>2025</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33">
         <v>9634</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33">
         <v>146</v>
       </c>
     </row>
@@ -12604,10 +12612,10 @@
       <c r="B34">
         <v>2016</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34">
         <v>1315</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34">
         <v>17</v>
       </c>
     </row>
@@ -12618,10 +12626,10 @@
       <c r="B35">
         <v>2017</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35">
         <v>1337</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35">
         <v>28</v>
       </c>
     </row>
@@ -12632,10 +12640,10 @@
       <c r="B36">
         <v>2018</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36">
         <v>1344</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36">
         <v>29</v>
       </c>
     </row>
@@ -12646,10 +12654,10 @@
       <c r="B37">
         <v>2019</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37">
         <v>1352</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37">
         <v>23</v>
       </c>
     </row>
@@ -12660,10 +12668,10 @@
       <c r="B38">
         <v>2020</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38">
         <v>1281</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38">
         <v>21</v>
       </c>
     </row>
@@ -12674,10 +12682,10 @@
       <c r="B39">
         <v>2021</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39">
         <v>1308</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39">
         <v>37</v>
       </c>
     </row>
@@ -12688,10 +12696,10 @@
       <c r="B40">
         <v>2022</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40">
         <v>1252</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40">
         <v>48</v>
       </c>
     </row>
@@ -12702,10 +12710,10 @@
       <c r="B41">
         <v>2023</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41">
         <v>1248</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41">
         <v>28</v>
       </c>
     </row>
@@ -12716,10 +12724,10 @@
       <c r="B42">
         <v>2024</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42">
         <v>1287</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42">
         <v>18</v>
       </c>
     </row>
@@ -12730,10 +12738,10 @@
       <c r="B43">
         <v>2025</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43">
         <v>1243</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43">
         <v>19</v>
       </c>
     </row>
@@ -12744,10 +12752,10 @@
       <c r="B44">
         <v>2016</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44">
         <v>22152</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44">
         <v>1808</v>
       </c>
     </row>
@@ -12758,10 +12766,10 @@
       <c r="B45">
         <v>2017</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45">
         <v>22324</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45">
         <v>1798</v>
       </c>
     </row>
@@ -12772,10 +12780,10 @@
       <c r="B46">
         <v>2018</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46">
         <v>22982</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46">
         <v>1853</v>
       </c>
     </row>
@@ -12786,10 +12794,10 @@
       <c r="B47">
         <v>2019</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47">
         <v>23690</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47">
         <v>1886</v>
       </c>
     </row>
@@ -12800,10 +12808,10 @@
       <c r="B48">
         <v>2020</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48">
         <v>22365</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48">
         <v>1876</v>
       </c>
     </row>
@@ -12814,10 +12822,10 @@
       <c r="B49">
         <v>2021</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49">
         <v>22891</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49">
         <v>1807</v>
       </c>
     </row>
@@ -12828,10 +12836,10 @@
       <c r="B50">
         <v>2022</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50">
         <v>23644</v>
       </c>
-      <c r="D50" s="12">
+      <c r="D50">
         <v>1841</v>
       </c>
     </row>
@@ -12842,10 +12850,10 @@
       <c r="B51">
         <v>2023</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51">
         <v>24344</v>
       </c>
-      <c r="D51" s="12">
+      <c r="D51">
         <v>1982</v>
       </c>
     </row>
@@ -12856,10 +12864,10 @@
       <c r="B52">
         <v>2024</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52">
         <v>24877</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52">
         <v>2026</v>
       </c>
     </row>
@@ -12870,10 +12878,10 @@
       <c r="B53">
         <v>2025</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53">
         <v>25522</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53">
         <v>2087</v>
       </c>
     </row>
@@ -12884,10 +12892,10 @@
       <c r="B54">
         <v>2016</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54">
         <v>13992</v>
       </c>
-      <c r="D54" s="12">
+      <c r="D54">
         <v>1454</v>
       </c>
     </row>
@@ -12898,10 +12906,10 @@
       <c r="B55">
         <v>2017</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55">
         <v>14284</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55">
         <v>1512</v>
       </c>
     </row>
@@ -12912,10 +12920,10 @@
       <c r="B56">
         <v>2018</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56">
         <v>14736</v>
       </c>
-      <c r="D56" s="12">
+      <c r="D56">
         <v>1502</v>
       </c>
     </row>
@@ -12926,10 +12934,10 @@
       <c r="B57">
         <v>2019</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57">
         <v>14878</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57">
         <v>1506</v>
       </c>
     </row>
@@ -12940,10 +12948,10 @@
       <c r="B58">
         <v>2020</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58">
         <v>13678</v>
       </c>
-      <c r="D58" s="12">
+      <c r="D58">
         <v>1403</v>
       </c>
     </row>
@@ -12954,10 +12962,10 @@
       <c r="B59">
         <v>2021</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59">
         <v>14027</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59">
         <v>1427</v>
       </c>
     </row>
@@ -12968,10 +12976,10 @@
       <c r="B60">
         <v>2022</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60">
         <v>15029</v>
       </c>
-      <c r="D60" s="12">
+      <c r="D60">
         <v>1439</v>
       </c>
     </row>
@@ -12982,10 +12990,10 @@
       <c r="B61">
         <v>2023</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61">
         <v>15508</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61">
         <v>1408</v>
       </c>
     </row>
@@ -12996,10 +13004,10 @@
       <c r="B62">
         <v>2024</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62">
         <v>15990</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62">
         <v>1349</v>
       </c>
     </row>
@@ -13010,10 +13018,10 @@
       <c r="B63">
         <v>2025</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63">
         <v>16012</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63">
         <v>1433</v>
       </c>
     </row>
@@ -13024,10 +13032,10 @@
       <c r="B64">
         <v>2016</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64">
         <v>9247</v>
       </c>
-      <c r="D64" s="12">
+      <c r="D64">
         <v>827</v>
       </c>
     </row>
@@ -13038,10 +13046,10 @@
       <c r="B65">
         <v>2017</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65">
         <v>9194</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65">
         <v>836</v>
       </c>
     </row>
@@ -13052,10 +13060,10 @@
       <c r="B66">
         <v>2018</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66">
         <v>9401</v>
       </c>
-      <c r="D66" s="12">
+      <c r="D66">
         <v>850</v>
       </c>
     </row>
@@ -13066,10 +13074,10 @@
       <c r="B67">
         <v>2019</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67">
         <v>9502</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67">
         <v>835</v>
       </c>
     </row>
@@ -13080,10 +13088,10 @@
       <c r="B68">
         <v>2020</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68">
         <v>8705</v>
       </c>
-      <c r="D68" s="12">
+      <c r="D68">
         <v>754</v>
       </c>
     </row>
@@ -13094,10 +13102,10 @@
       <c r="B69">
         <v>2021</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69">
         <v>8986</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69">
         <v>668</v>
       </c>
     </row>
@@ -13108,10 +13116,10 @@
       <c r="B70">
         <v>2022</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70">
         <v>9305</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70">
         <v>741</v>
       </c>
     </row>
@@ -13122,10 +13130,10 @@
       <c r="B71">
         <v>2023</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71">
         <v>9599</v>
       </c>
-      <c r="D71" s="12">
+      <c r="D71">
         <v>772</v>
       </c>
     </row>
@@ -13136,10 +13144,10 @@
       <c r="B72">
         <v>2024</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72">
         <v>9213</v>
       </c>
-      <c r="D72" s="12">
+      <c r="D72">
         <v>713</v>
       </c>
     </row>
@@ -13150,10 +13158,10 @@
       <c r="B73">
         <v>2025</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73">
         <v>9328</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73">
         <v>694</v>
       </c>
     </row>
@@ -13164,10 +13172,10 @@
       <c r="B74">
         <v>2016</v>
       </c>
-      <c r="C74" s="12">
+      <c r="C74">
         <v>27388</v>
       </c>
-      <c r="D74" s="12">
+      <c r="D74">
         <v>677</v>
       </c>
     </row>
@@ -13178,10 +13186,10 @@
       <c r="B75">
         <v>2017</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75">
         <v>28070</v>
       </c>
-      <c r="D75" s="12">
+      <c r="D75">
         <v>703</v>
       </c>
     </row>
@@ -13192,10 +13200,10 @@
       <c r="B76">
         <v>2018</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76">
         <v>28493</v>
       </c>
-      <c r="D76" s="12">
+      <c r="D76">
         <v>674</v>
       </c>
     </row>
@@ -13206,10 +13214,10 @@
       <c r="B77">
         <v>2019</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77">
         <v>29527</v>
       </c>
-      <c r="D77" s="12">
+      <c r="D77">
         <v>699</v>
       </c>
     </row>
@@ -13220,10 +13228,10 @@
       <c r="B78">
         <v>2020</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78">
         <v>25624</v>
       </c>
-      <c r="D78" s="12">
+      <c r="D78">
         <v>489</v>
       </c>
     </row>
@@ -13234,10 +13242,10 @@
       <c r="B79">
         <v>2021</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79">
         <v>27345</v>
       </c>
-      <c r="D79" s="12">
+      <c r="D79">
         <v>556</v>
       </c>
     </row>
@@ -13248,10 +13256,10 @@
       <c r="B80">
         <v>2022</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80">
         <v>29140</v>
       </c>
-      <c r="D80" s="12">
+      <c r="D80">
         <v>653</v>
       </c>
     </row>
@@ -13262,10 +13270,10 @@
       <c r="B81">
         <v>2023</v>
       </c>
-      <c r="C81" s="12">
+      <c r="C81">
         <v>29991</v>
       </c>
-      <c r="D81" s="12">
+      <c r="D81">
         <v>706</v>
       </c>
     </row>
@@ -13276,10 +13284,10 @@
       <c r="B82">
         <v>2024</v>
       </c>
-      <c r="C82" s="12">
+      <c r="C82">
         <v>29695</v>
       </c>
-      <c r="D82" s="12">
+      <c r="D82">
         <v>661</v>
       </c>
     </row>
@@ -13290,10 +13298,10 @@
       <c r="B83">
         <v>2025</v>
       </c>
-      <c r="C83" s="12">
+      <c r="C83">
         <v>30287</v>
       </c>
-      <c r="D83" s="12">
+      <c r="D83">
         <v>736</v>
       </c>
     </row>
@@ -13304,10 +13312,10 @@
       <c r="B84">
         <v>2016</v>
       </c>
-      <c r="C84" s="12">
+      <c r="C84">
         <v>2159</v>
       </c>
-      <c r="D84" s="12">
+      <c r="D84">
         <v>211</v>
       </c>
     </row>
@@ -13318,10 +13326,10 @@
       <c r="B85">
         <v>2017</v>
       </c>
-      <c r="C85" s="12">
+      <c r="C85">
         <v>2195</v>
       </c>
-      <c r="D85" s="12">
+      <c r="D85">
         <v>233</v>
       </c>
     </row>
@@ -13332,10 +13340,10 @@
       <c r="B86">
         <v>2018</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C86">
         <v>2209</v>
       </c>
-      <c r="D86" s="12">
+      <c r="D86">
         <v>238</v>
       </c>
     </row>
@@ -13346,10 +13354,10 @@
       <c r="B87">
         <v>2019</v>
       </c>
-      <c r="C87" s="12">
+      <c r="C87">
         <v>2044</v>
       </c>
-      <c r="D87" s="12">
+      <c r="D87">
         <v>233</v>
       </c>
     </row>
@@ -13360,10 +13368,10 @@
       <c r="B88">
         <v>2020</v>
       </c>
-      <c r="C88" s="12">
+      <c r="C88">
         <v>1799</v>
       </c>
-      <c r="D88" s="12">
+      <c r="D88">
         <v>189</v>
       </c>
     </row>
@@ -13374,10 +13382,10 @@
       <c r="B89">
         <v>2021</v>
       </c>
-      <c r="C89" s="12">
+      <c r="C89">
         <v>1874</v>
       </c>
-      <c r="D89" s="12">
+      <c r="D89">
         <v>211</v>
       </c>
     </row>
@@ -13388,10 +13396,10 @@
       <c r="B90">
         <v>2022</v>
       </c>
-      <c r="C90" s="12">
+      <c r="C90">
         <v>1906</v>
       </c>
-      <c r="D90" s="12">
+      <c r="D90">
         <v>192</v>
       </c>
     </row>
@@ -13402,10 +13410,10 @@
       <c r="B91">
         <v>2023</v>
       </c>
-      <c r="C91" s="12">
+      <c r="C91">
         <v>2124</v>
       </c>
-      <c r="D91" s="12">
+      <c r="D91">
         <v>177</v>
       </c>
     </row>
@@ -13416,10 +13424,10 @@
       <c r="B92">
         <v>2024</v>
       </c>
-      <c r="C92" s="12">
+      <c r="C92">
         <v>1629</v>
       </c>
-      <c r="D92" s="12">
+      <c r="D92">
         <v>116</v>
       </c>
     </row>
@@ -13430,10 +13438,10 @@
       <c r="B93">
         <v>2025</v>
       </c>
-      <c r="C93" s="12">
+      <c r="C93">
         <v>1949</v>
       </c>
-      <c r="D93" s="12">
+      <c r="D93">
         <v>150</v>
       </c>
     </row>
@@ -13444,10 +13452,10 @@
       <c r="B94">
         <v>2016</v>
       </c>
-      <c r="C94" s="12">
+      <c r="C94">
         <v>5073</v>
       </c>
-      <c r="D94" s="12">
+      <c r="D94">
         <v>935</v>
       </c>
     </row>
@@ -13458,10 +13466,10 @@
       <c r="B95">
         <v>2017</v>
       </c>
-      <c r="C95" s="12">
+      <c r="C95">
         <v>5205</v>
       </c>
-      <c r="D95" s="12">
+      <c r="D95">
         <v>903</v>
       </c>
     </row>
@@ -13472,10 +13480,10 @@
       <c r="B96">
         <v>2018</v>
       </c>
-      <c r="C96" s="12">
+      <c r="C96">
         <v>5410</v>
       </c>
-      <c r="D96" s="12">
+      <c r="D96">
         <v>904</v>
       </c>
     </row>
@@ -13486,10 +13494,10 @@
       <c r="B97">
         <v>2019</v>
       </c>
-      <c r="C97" s="12">
+      <c r="C97">
         <v>5659</v>
       </c>
-      <c r="D97" s="12">
+      <c r="D97">
         <v>912</v>
       </c>
     </row>
@@ -13500,10 +13508,10 @@
       <c r="B98">
         <v>2020</v>
       </c>
-      <c r="C98" s="12">
+      <c r="C98">
         <v>5377</v>
       </c>
-      <c r="D98" s="12">
+      <c r="D98">
         <v>916</v>
       </c>
     </row>
@@ -13514,10 +13522,10 @@
       <c r="B99">
         <v>2021</v>
       </c>
-      <c r="C99" s="12">
+      <c r="C99">
         <v>6055</v>
       </c>
-      <c r="D99" s="12">
+      <c r="D99">
         <v>889</v>
       </c>
     </row>
@@ -13528,10 +13536,10 @@
       <c r="B100">
         <v>2022</v>
       </c>
-      <c r="C100" s="12">
+      <c r="C100">
         <v>6596</v>
       </c>
-      <c r="D100" s="12">
+      <c r="D100">
         <v>958</v>
       </c>
     </row>
@@ -13542,10 +13550,10 @@
       <c r="B101">
         <v>2023</v>
       </c>
-      <c r="C101" s="12">
+      <c r="C101">
         <v>6495</v>
       </c>
-      <c r="D101" s="12">
+      <c r="D101">
         <v>1031</v>
       </c>
     </row>
@@ -13556,10 +13564,10 @@
       <c r="B102">
         <v>2024</v>
       </c>
-      <c r="C102" s="12">
+      <c r="C102">
         <v>6387</v>
       </c>
-      <c r="D102" s="12">
+      <c r="D102">
         <v>1006</v>
       </c>
     </row>
@@ -13570,10 +13578,10 @@
       <c r="B103">
         <v>2025</v>
       </c>
-      <c r="C103" s="12">
+      <c r="C103">
         <v>6558</v>
       </c>
-      <c r="D103" s="12">
+      <c r="D103">
         <v>895</v>
       </c>
     </row>
@@ -13584,10 +13592,10 @@
       <c r="B104">
         <v>2016</v>
       </c>
-      <c r="C104" s="12">
+      <c r="C104">
         <v>20684</v>
       </c>
-      <c r="D104" s="12">
+      <c r="D104">
         <v>7120</v>
       </c>
     </row>
@@ -13598,10 +13606,10 @@
       <c r="B105">
         <v>2017</v>
       </c>
-      <c r="C105" s="12">
+      <c r="C105">
         <v>20956</v>
       </c>
-      <c r="D105" s="12">
+      <c r="D105">
         <v>7216</v>
       </c>
     </row>
@@ -13612,10 +13620,10 @@
       <c r="B106">
         <v>2018</v>
       </c>
-      <c r="C106" s="12">
+      <c r="C106">
         <v>21131</v>
       </c>
-      <c r="D106" s="12">
+      <c r="D106">
         <v>7167</v>
       </c>
     </row>
@@ -13626,10 +13634,10 @@
       <c r="B107">
         <v>2019</v>
       </c>
-      <c r="C107" s="12">
+      <c r="C107">
         <v>21023</v>
       </c>
-      <c r="D107" s="12">
+      <c r="D107">
         <v>7067</v>
       </c>
     </row>
@@ -13640,10 +13648,10 @@
       <c r="B108">
         <v>2020</v>
       </c>
-      <c r="C108" s="12">
+      <c r="C108">
         <v>20632</v>
       </c>
-      <c r="D108" s="12">
+      <c r="D108">
         <v>7173</v>
       </c>
     </row>
@@ -13654,10 +13662,10 @@
       <c r="B109">
         <v>2021</v>
       </c>
-      <c r="C109" s="12">
+      <c r="C109">
         <v>20626</v>
       </c>
-      <c r="D109" s="12">
+      <c r="D109">
         <v>6983</v>
       </c>
     </row>
@@ -13668,10 +13676,10 @@
       <c r="B110">
         <v>2022</v>
       </c>
-      <c r="C110" s="12">
+      <c r="C110">
         <v>21317</v>
       </c>
-      <c r="D110" s="12">
+      <c r="D110">
         <v>7062</v>
       </c>
     </row>
@@ -13682,10 +13690,10 @@
       <c r="B111">
         <v>2023</v>
       </c>
-      <c r="C111" s="12">
+      <c r="C111">
         <v>21576</v>
       </c>
-      <c r="D111" s="12">
+      <c r="D111">
         <v>7010</v>
       </c>
     </row>
@@ -13696,10 +13704,10 @@
       <c r="B112">
         <v>2024</v>
       </c>
-      <c r="C112" s="12">
+      <c r="C112">
         <v>21838</v>
       </c>
-      <c r="D112" s="12">
+      <c r="D112">
         <v>7025</v>
       </c>
     </row>
@@ -13710,10 +13718,10 @@
       <c r="B113">
         <v>2025</v>
       </c>
-      <c r="C113" s="12">
+      <c r="C113">
         <v>22100</v>
       </c>
-      <c r="D113" s="12">
+      <c r="D113">
         <v>7281</v>
       </c>
     </row>
@@ -13721,10 +13729,10 @@
       <c r="A114" t="s">
         <v>57</v>
       </c>
-      <c r="C114" s="12">
+      <c r="C114">
         <v>1397753</v>
       </c>
-      <c r="D114" s="12">
+      <c r="D114">
         <v>144464</v>
       </c>
     </row>
@@ -13776,7 +13784,7 @@
       <c r="D2">
         <v>1248</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="12">
         <f>D2/C2</f>
         <v>5.1889734314581513E-2</v>
       </c>
@@ -13794,7 +13802,7 @@
       <c r="D3">
         <v>1331</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <f t="shared" ref="E3:E66" si="0">D3/C3</f>
         <v>5.4875283446712018E-2</v>
       </c>
@@ -13812,7 +13820,7 @@
       <c r="D4">
         <v>1296</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <f t="shared" si="0"/>
         <v>5.3562572326004296E-2</v>
       </c>
@@ -13830,7 +13838,7 @@
       <c r="D5">
         <v>1196</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f t="shared" si="0"/>
         <v>5.0504623960136816E-2</v>
       </c>
@@ -13848,7 +13856,7 @@
       <c r="D6">
         <v>1215</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f t="shared" si="0"/>
         <v>5.3784860557768925E-2</v>
       </c>
@@ -13866,7 +13874,7 @@
       <c r="D7">
         <v>1183</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f t="shared" si="0"/>
         <v>5.0951847704367302E-2</v>
       </c>
@@ -13884,7 +13892,7 @@
       <c r="D8">
         <v>1140</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <f t="shared" si="0"/>
         <v>4.9267470504343318E-2</v>
       </c>
@@ -13902,7 +13910,7 @@
       <c r="D9">
         <v>1109</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <f t="shared" si="0"/>
         <v>4.7525176773087638E-2</v>
       </c>
@@ -13920,7 +13928,7 @@
       <c r="D10">
         <v>1143</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <f t="shared" si="0"/>
         <v>4.9456968543117999E-2</v>
       </c>
@@ -13938,7 +13946,7 @@
       <c r="D11">
         <v>1193</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <f t="shared" si="0"/>
         <v>5.1611507678996325E-2</v>
       </c>
@@ -13956,7 +13964,7 @@
       <c r="D12">
         <v>43</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <f t="shared" si="0"/>
         <v>5.6209150326797387E-2</v>
       </c>
@@ -13974,7 +13982,7 @@
       <c r="D13">
         <v>32</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f t="shared" si="0"/>
         <v>4.3537414965986392E-2</v>
       </c>
@@ -13992,7 +14000,7 @@
       <c r="D14">
         <v>34</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <f t="shared" si="0"/>
         <v>4.7156726768377254E-2</v>
       </c>
@@ -14010,7 +14018,7 @@
       <c r="D15">
         <v>28</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <f t="shared" si="0"/>
         <v>3.9436619718309862E-2</v>
       </c>
@@ -14028,7 +14036,7 @@
       <c r="D16">
         <v>37</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <f t="shared" si="0"/>
         <v>5.6402439024390245E-2</v>
       </c>
@@ -14046,7 +14054,7 @@
       <c r="D17">
         <v>32</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <f t="shared" si="0"/>
         <v>5.7040998217468802E-2</v>
       </c>
@@ -14064,7 +14072,7 @@
       <c r="D18">
         <v>36</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <f t="shared" si="0"/>
         <v>6.4748201438848921E-2</v>
       </c>
@@ -14082,7 +14090,7 @@
       <c r="D19">
         <v>25</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="12">
         <f t="shared" si="0"/>
         <v>4.3327556325823226E-2</v>
       </c>
@@ -14100,7 +14108,7 @@
       <c r="D20">
         <v>35</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <f t="shared" si="0"/>
         <v>6.5055762081784388E-2</v>
       </c>
@@ -14118,7 +14126,7 @@
       <c r="D21">
         <v>23</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <f t="shared" si="0"/>
         <v>4.7227926078028747E-2</v>
       </c>
@@ -14136,7 +14144,7 @@
       <c r="D22">
         <v>205</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="12">
         <f t="shared" si="0"/>
         <v>2.2871806314849939E-2</v>
       </c>
@@ -14154,7 +14162,7 @@
       <c r="D23">
         <v>218</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="12">
         <f t="shared" si="0"/>
         <v>2.4040582267313631E-2</v>
       </c>
@@ -14172,7 +14180,7 @@
       <c r="D24">
         <v>193</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="12">
         <f t="shared" si="0"/>
         <v>2.1095201661383758E-2</v>
       </c>
@@ -14190,7 +14198,7 @@
       <c r="D25">
         <v>182</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="12">
         <f t="shared" si="0"/>
         <v>1.9436138402392139E-2</v>
       </c>
@@ -14208,7 +14216,7 @@
       <c r="D26">
         <v>170</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="12">
         <f t="shared" si="0"/>
         <v>1.8664909969257796E-2</v>
       </c>
@@ -14226,7 +14234,7 @@
       <c r="D27">
         <v>205</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="12">
         <f t="shared" si="0"/>
         <v>2.2524997253049114E-2</v>
       </c>
@@ -14244,7 +14252,7 @@
       <c r="D28">
         <v>170</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="12">
         <f t="shared" si="0"/>
         <v>1.8209083119108824E-2</v>
       </c>
@@ -14262,7 +14270,7 @@
       <c r="D29">
         <v>162</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="12">
         <f t="shared" si="0"/>
         <v>1.7449375269280483E-2</v>
       </c>
@@ -14280,7 +14288,7 @@
       <c r="D30">
         <v>122</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="12">
         <f t="shared" si="0"/>
         <v>1.321633625826021E-2</v>
       </c>
@@ -14298,7 +14306,7 @@
       <c r="D31">
         <v>146</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="12">
         <f t="shared" si="0"/>
         <v>1.515466057712269E-2</v>
       </c>
@@ -14316,7 +14324,7 @@
       <c r="D32">
         <v>17</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="12">
         <f t="shared" si="0"/>
         <v>1.2927756653992395E-2</v>
       </c>
@@ -14334,7 +14342,7 @@
       <c r="D33">
         <v>28</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="12">
         <f t="shared" si="0"/>
         <v>2.0942408376963352E-2</v>
       </c>
@@ -14352,7 +14360,7 @@
       <c r="D34">
         <v>29</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="12">
         <f t="shared" si="0"/>
         <v>2.1577380952380952E-2</v>
       </c>
@@ -14370,7 +14378,7 @@
       <c r="D35">
         <v>23</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="12">
         <f t="shared" si="0"/>
         <v>1.7011834319526627E-2</v>
       </c>
@@ -14388,7 +14396,7 @@
       <c r="D36">
         <v>21</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="12">
         <f t="shared" si="0"/>
         <v>1.6393442622950821E-2</v>
       </c>
@@ -14406,7 +14414,7 @@
       <c r="D37">
         <v>37</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="12">
         <f t="shared" si="0"/>
         <v>2.8287461773700305E-2</v>
       </c>
@@ -14424,7 +14432,7 @@
       <c r="D38">
         <v>48</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="12">
         <f t="shared" si="0"/>
         <v>3.8338658146964855E-2</v>
       </c>
@@ -14442,7 +14450,7 @@
       <c r="D39">
         <v>28</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="12">
         <f t="shared" si="0"/>
         <v>2.2435897435897436E-2</v>
       </c>
@@ -14460,7 +14468,7 @@
       <c r="D40">
         <v>18</v>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="12">
         <f t="shared" si="0"/>
         <v>1.3986013986013986E-2</v>
       </c>
@@ -14478,7 +14486,7 @@
       <c r="D41">
         <v>19</v>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="12">
         <f t="shared" si="0"/>
         <v>1.5285599356395816E-2</v>
       </c>
@@ -14496,7 +14504,7 @@
       <c r="D42">
         <v>1808</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="12">
         <f t="shared" si="0"/>
         <v>8.1617912603828099E-2</v>
       </c>
@@ -14514,7 +14522,7 @@
       <c r="D43">
         <v>1798</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="12">
         <f t="shared" si="0"/>
         <v>8.0541121662784446E-2</v>
       </c>
@@ -14532,7 +14540,7 @@
       <c r="D44">
         <v>1853</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="12">
         <f t="shared" si="0"/>
         <v>8.062831781394135E-2</v>
       </c>
@@ -14550,7 +14558,7 @@
       <c r="D45">
         <v>1886</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="12">
         <f t="shared" si="0"/>
         <v>7.9611650485436891E-2</v>
       </c>
@@ -14568,7 +14576,7 @@
       <c r="D46">
         <v>1876</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="12">
         <f t="shared" si="0"/>
         <v>8.3881064162754301E-2</v>
       </c>
@@ -14586,7 +14594,7 @@
       <c r="D47">
         <v>1807</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="12">
         <f t="shared" si="0"/>
         <v>7.8939321130575335E-2</v>
       </c>
@@ -14604,7 +14612,7 @@
       <c r="D48">
         <v>1841</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="12">
         <f t="shared" si="0"/>
         <v>7.7863305701234981E-2</v>
       </c>
@@ -14622,7 +14630,7 @@
       <c r="D49">
         <v>1982</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="12">
         <f t="shared" si="0"/>
         <v>8.141636542885311E-2</v>
       </c>
@@ -14640,7 +14648,7 @@
       <c r="D50">
         <v>2026</v>
       </c>
-      <c r="E50" s="13">
+      <c r="E50" s="12">
         <f t="shared" si="0"/>
         <v>8.1440688185874507E-2</v>
       </c>
@@ -14658,7 +14666,7 @@
       <c r="D51">
         <v>2087</v>
       </c>
-      <c r="E51" s="13">
+      <c r="E51" s="12">
         <f t="shared" si="0"/>
         <v>8.1772588355144588E-2</v>
       </c>
@@ -14676,7 +14684,7 @@
       <c r="D52">
         <v>1454</v>
       </c>
-      <c r="E52" s="13">
+      <c r="E52" s="12">
         <f t="shared" si="0"/>
         <v>0.10391652372784448</v>
       </c>
@@ -14694,7 +14702,7 @@
       <c r="D53">
         <v>1512</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53" s="12">
         <f t="shared" si="0"/>
         <v>0.10585270232427892</v>
       </c>
@@ -14712,7 +14720,7 @@
       <c r="D54">
         <v>1502</v>
       </c>
-      <c r="E54" s="13">
+      <c r="E54" s="12">
         <f t="shared" si="0"/>
         <v>0.10192725298588491</v>
       </c>
@@ -14730,7 +14738,7 @@
       <c r="D55">
         <v>1506</v>
       </c>
-      <c r="E55" s="13">
+      <c r="E55" s="12">
         <f t="shared" si="0"/>
         <v>0.10122328269928754</v>
       </c>
@@ -14748,7 +14756,7 @@
       <c r="D56">
         <v>1403</v>
       </c>
-      <c r="E56" s="13">
+      <c r="E56" s="12">
         <f t="shared" si="0"/>
         <v>0.10257347565433543</v>
       </c>
@@ -14766,7 +14774,7 @@
       <c r="D57">
         <v>1427</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E57" s="12">
         <f t="shared" si="0"/>
         <v>0.10173237328010266</v>
       </c>
@@ -14784,7 +14792,7 @@
       <c r="D58">
         <v>1439</v>
       </c>
-      <c r="E58" s="13">
+      <c r="E58" s="12">
         <f t="shared" si="0"/>
         <v>9.5748220107791604E-2</v>
       </c>
@@ -14802,7 +14810,7 @@
       <c r="D59">
         <v>1408</v>
       </c>
-      <c r="E59" s="13">
+      <c r="E59" s="12">
         <f t="shared" si="0"/>
         <v>9.0791849368068098E-2</v>
       </c>
@@ -14820,7 +14828,7 @@
       <c r="D60">
         <v>1349</v>
       </c>
-      <c r="E60" s="13">
+      <c r="E60" s="12">
         <f t="shared" si="0"/>
         <v>8.4365228267667292E-2</v>
       </c>
@@ -14838,7 +14846,7 @@
       <c r="D61">
         <v>1433</v>
       </c>
-      <c r="E61" s="13">
+      <c r="E61" s="12">
         <f t="shared" si="0"/>
         <v>8.9495378466150383E-2</v>
       </c>
@@ -14856,7 +14864,7 @@
       <c r="D62">
         <v>827</v>
       </c>
-      <c r="E62" s="13">
+      <c r="E62" s="12">
         <f t="shared" si="0"/>
         <v>8.9434411160376343E-2</v>
       </c>
@@ -14874,7 +14882,7 @@
       <c r="D63">
         <v>836</v>
       </c>
-      <c r="E63" s="13">
+      <c r="E63" s="12">
         <f t="shared" si="0"/>
         <v>9.0928866652164458E-2</v>
       </c>
@@ -14892,7 +14900,7 @@
       <c r="D64">
         <v>850</v>
       </c>
-      <c r="E64" s="13">
+      <c r="E64" s="12">
         <f t="shared" si="0"/>
         <v>9.0415913200723327E-2</v>
       </c>
@@ -14910,7 +14918,7 @@
       <c r="D65">
         <v>835</v>
       </c>
-      <c r="E65" s="13">
+      <c r="E65" s="12">
         <f t="shared" si="0"/>
         <v>8.7876236581772252E-2</v>
       </c>
@@ -14928,7 +14936,7 @@
       <c r="D66">
         <v>754</v>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="12">
         <f t="shared" si="0"/>
         <v>8.6616886846639859E-2</v>
       </c>
@@ -14946,7 +14954,7 @@
       <c r="D67">
         <v>668</v>
       </c>
-      <c r="E67" s="13">
+      <c r="E67" s="12">
         <f t="shared" ref="E67:E101" si="1">D67/C67</f>
         <v>7.4337858891609168E-2</v>
       </c>
@@ -14964,7 +14972,7 @@
       <c r="D68">
         <v>741</v>
       </c>
-      <c r="E68" s="13">
+      <c r="E68" s="12">
         <f t="shared" si="1"/>
         <v>7.963460505104783E-2</v>
       </c>
@@ -14982,7 +14990,7 @@
       <c r="D69">
         <v>772</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="12">
         <f t="shared" si="1"/>
         <v>8.0425044275445362E-2</v>
       </c>
@@ -15000,7 +15008,7 @@
       <c r="D70">
         <v>713</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="12">
         <f t="shared" si="1"/>
         <v>7.7390643655703903E-2</v>
       </c>
@@ -15018,7 +15026,7 @@
       <c r="D71">
         <v>694</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="12">
         <f t="shared" si="1"/>
         <v>7.4399656946826764E-2</v>
       </c>
@@ -15036,7 +15044,7 @@
       <c r="D72">
         <v>677</v>
       </c>
-      <c r="E72" s="13">
+      <c r="E72" s="12">
         <f t="shared" si="1"/>
         <v>2.4718854972980868E-2</v>
       </c>
@@ -15054,7 +15062,7 @@
       <c r="D73">
         <v>703</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73" s="12">
         <f t="shared" si="1"/>
         <v>2.5044531528322051E-2</v>
       </c>
@@ -15072,7 +15080,7 @@
       <c r="D74">
         <v>674</v>
       </c>
-      <c r="E74" s="13">
+      <c r="E74" s="12">
         <f t="shared" si="1"/>
         <v>2.3654932790509949E-2</v>
       </c>
@@ -15090,7 +15098,7 @@
       <c r="D75">
         <v>699</v>
       </c>
-      <c r="E75" s="13">
+      <c r="E75" s="12">
         <f t="shared" si="1"/>
         <v>2.3673248213499511E-2</v>
       </c>
@@ -15108,7 +15116,7 @@
       <c r="D76">
         <v>489</v>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="12">
         <f t="shared" si="1"/>
         <v>1.9083671557914454E-2</v>
       </c>
@@ -15126,7 +15134,7 @@
       <c r="D77">
         <v>556</v>
       </c>
-      <c r="E77" s="13">
+      <c r="E77" s="12">
         <f t="shared" si="1"/>
         <v>2.0332784786981167E-2</v>
       </c>
@@ -15144,7 +15152,7 @@
       <c r="D78">
         <v>653</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="12">
         <f t="shared" si="1"/>
         <v>2.2409059711736446E-2</v>
       </c>
@@ -15162,7 +15170,7 @@
       <c r="D79">
         <v>706</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="12">
         <f t="shared" si="1"/>
         <v>2.3540395451968923E-2</v>
       </c>
@@ -15180,7 +15188,7 @@
       <c r="D80">
         <v>661</v>
       </c>
-      <c r="E80" s="13">
+      <c r="E80" s="12">
         <f t="shared" si="1"/>
         <v>2.2259639669978112E-2</v>
       </c>
@@ -15198,7 +15206,7 @@
       <c r="D81">
         <v>736</v>
       </c>
-      <c r="E81" s="13">
+      <c r="E81" s="12">
         <f t="shared" si="1"/>
         <v>2.4300855152375608E-2</v>
       </c>
@@ -15216,7 +15224,7 @@
       <c r="D82">
         <v>211</v>
       </c>
-      <c r="E82" s="13">
+      <c r="E82" s="12">
         <f t="shared" si="1"/>
         <v>9.7730430754979156E-2</v>
       </c>
@@ -15234,7 +15242,7 @@
       <c r="D83">
         <v>233</v>
       </c>
-      <c r="E83" s="13">
+      <c r="E83" s="12">
         <f t="shared" si="1"/>
         <v>0.1061503416856492</v>
       </c>
@@ -15252,7 +15260,7 @@
       <c r="D84">
         <v>238</v>
       </c>
-      <c r="E84" s="13">
+      <c r="E84" s="12">
         <f t="shared" si="1"/>
         <v>0.10774105930285197</v>
       </c>
@@ -15270,7 +15278,7 @@
       <c r="D85">
         <v>233</v>
       </c>
-      <c r="E85" s="13">
+      <c r="E85" s="12">
         <f t="shared" si="1"/>
         <v>0.11399217221135029</v>
       </c>
@@ -15288,7 +15296,7 @@
       <c r="D86">
         <v>189</v>
       </c>
-      <c r="E86" s="13">
+      <c r="E86" s="12">
         <f t="shared" si="1"/>
         <v>0.10505836575875487</v>
       </c>
@@ -15306,7 +15314,7 @@
       <c r="D87">
         <v>211</v>
       </c>
-      <c r="E87" s="13">
+      <c r="E87" s="12">
         <f t="shared" si="1"/>
         <v>0.11259338313767342</v>
       </c>
@@ -15324,7 +15332,7 @@
       <c r="D88">
         <v>192</v>
       </c>
-      <c r="E88" s="13">
+      <c r="E88" s="12">
         <f t="shared" si="1"/>
         <v>0.10073452256033578</v>
       </c>
@@ -15342,7 +15350,7 @@
       <c r="D89">
         <v>177</v>
       </c>
-      <c r="E89" s="13">
+      <c r="E89" s="12">
         <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -15360,7 +15368,7 @@
       <c r="D90">
         <v>116</v>
       </c>
-      <c r="E90" s="13">
+      <c r="E90" s="12">
         <f t="shared" si="1"/>
         <v>7.1209330877839164E-2</v>
       </c>
@@ -15378,7 +15386,7 @@
       <c r="D91">
         <v>150</v>
       </c>
-      <c r="E91" s="13">
+      <c r="E91" s="12">
         <f t="shared" si="1"/>
         <v>7.6962544894817853E-2</v>
       </c>
@@ -15396,7 +15404,7 @@
       <c r="D92">
         <v>935</v>
       </c>
-      <c r="E92" s="13">
+      <c r="E92" s="12">
         <f t="shared" si="1"/>
         <v>0.18430908732505422</v>
       </c>
@@ -15414,7 +15422,7 @@
       <c r="D93">
         <v>903</v>
       </c>
-      <c r="E93" s="13">
+      <c r="E93" s="12">
         <f t="shared" si="1"/>
         <v>0.17348703170028817</v>
       </c>
@@ -15432,7 +15440,7 @@
       <c r="D94">
         <v>904</v>
       </c>
-      <c r="E94" s="13">
+      <c r="E94" s="12">
         <f t="shared" si="1"/>
         <v>0.16709796672828095</v>
       </c>
@@ -15450,7 +15458,7 @@
       <c r="D95">
         <v>912</v>
       </c>
-      <c r="E95" s="13">
+      <c r="E95" s="12">
         <f t="shared" si="1"/>
         <v>0.16115921540908287</v>
       </c>
@@ -15468,7 +15476,7 @@
       <c r="D96">
         <v>916</v>
       </c>
-      <c r="E96" s="13">
+      <c r="E96" s="12">
         <f t="shared" si="1"/>
         <v>0.17035521666356704</v>
       </c>
@@ -15486,7 +15494,7 @@
       <c r="D97">
         <v>889</v>
       </c>
-      <c r="E97" s="13">
+      <c r="E97" s="12">
         <f t="shared" si="1"/>
         <v>0.14682080924855492</v>
       </c>
@@ -15504,7 +15512,7 @@
       <c r="D98">
         <v>958</v>
       </c>
-      <c r="E98" s="13">
+      <c r="E98" s="12">
         <f t="shared" si="1"/>
         <v>0.14523953911461493</v>
       </c>
@@ -15522,7 +15530,7 @@
       <c r="D99">
         <v>1031</v>
       </c>
-      <c r="E99" s="13">
+      <c r="E99" s="12">
         <f t="shared" si="1"/>
         <v>0.15873749037721324</v>
       </c>
@@ -15540,7 +15548,7 @@
       <c r="D100">
         <v>1006</v>
       </c>
-      <c r="E100" s="13">
+      <c r="E100" s="12">
         <f t="shared" si="1"/>
         <v>0.1575074369813684</v>
       </c>
@@ -15558,7 +15566,7 @@
       <c r="D101">
         <v>895</v>
       </c>
-      <c r="E101" s="13">
+      <c r="E101" s="12">
         <f t="shared" si="1"/>
         <v>0.13647453491918268</v>
       </c>
